--- a/Data/Figure2/Weight/Weight-GTT.xlsx
+++ b/Data/Figure2/Weight/Weight-GTT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure2\Weight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C985A92E-3265-4A90-8FDB-2990B11C9F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7536F624-379A-4C1E-B7C8-F37B48CAD39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9516,952 +9516,952 @@
       <c r="A292" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B292" s="1">
+      <c r="B292" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C292" s="1">
+        <v>0</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E292" s="1">
         <v>21.2</v>
-      </c>
-      <c r="C292" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E292" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B293" s="1">
+      <c r="B293" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C293" s="1">
+        <v>1</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E293" s="1">
         <v>21.4</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E293" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B294" s="1">
+      <c r="B294" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C294" s="1">
+        <v>2</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E294" s="1">
         <v>21.7</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E294" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B295" s="1">
+      <c r="B295" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C295" s="1">
+        <v>3</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E295" s="1">
         <v>21.8</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E295" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B296" s="1">
+      <c r="B296" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C296" s="1">
+        <v>4</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E296" s="1">
         <v>22.8</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E296" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B297" s="1">
+      <c r="B297" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C297" s="1">
+        <v>5</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E297" s="1">
         <v>22.8</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E297" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B298" s="1">
+      <c r="B298" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C298" s="1">
+        <v>6</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E298" s="1">
         <v>23</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E298" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B299" s="1">
+      <c r="B299" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C299" s="1">
+        <v>0</v>
+      </c>
+      <c r="D299" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E299" s="1">
         <v>24</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E299" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B300" s="1">
+      <c r="B300" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C300" s="1">
+        <v>1</v>
+      </c>
+      <c r="D300" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E300" s="1">
         <v>24.5</v>
-      </c>
-      <c r="C300" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E300" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B301" s="1">
+      <c r="B301" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C301" s="1">
+        <v>2</v>
+      </c>
+      <c r="D301" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E301" s="1">
         <v>24.4</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E301" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B302" s="1">
+      <c r="B302" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C302" s="1">
+        <v>3</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E302" s="1">
         <v>24.3</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E302" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B303" s="1">
+      <c r="B303" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C303" s="1">
+        <v>4</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E303" s="1">
         <v>27</v>
-      </c>
-      <c r="C303" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E303" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B304" s="1">
+      <c r="B304" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C304" s="1">
+        <v>5</v>
+      </c>
+      <c r="D304" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E304" s="1">
         <v>27</v>
-      </c>
-      <c r="C304" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E304" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B305" s="1">
+      <c r="B305" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C305" s="1">
+        <v>6</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E305" s="1">
         <v>26</v>
-      </c>
-      <c r="C305" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E305" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B306" s="1">
+      <c r="B306" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C306" s="1">
+        <v>0</v>
+      </c>
+      <c r="D306" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E306" s="1">
         <v>24.9</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E306" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B307" s="1">
+      <c r="B307" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C307" s="1">
+        <v>1</v>
+      </c>
+      <c r="D307" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E307" s="1">
         <v>25.2</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E307" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B308" s="1">
+      <c r="B308" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C308" s="1">
+        <v>2</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E308" s="1">
         <v>25.9</v>
-      </c>
-      <c r="C308" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E308" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B309" s="1">
+      <c r="B309" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C309" s="1">
+        <v>3</v>
+      </c>
+      <c r="D309" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E309" s="1">
         <v>25.8</v>
-      </c>
-      <c r="C309" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E309" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B310" s="1">
+      <c r="B310" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C310" s="1">
+        <v>4</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E310" s="1">
         <v>26.2</v>
-      </c>
-      <c r="C310" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E310" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B311" s="1">
+      <c r="B311" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C311" s="1">
+        <v>5</v>
+      </c>
+      <c r="D311" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E311" s="1">
         <v>26.2</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D311" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E311" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B312" s="1">
+      <c r="B312" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C312" s="1">
+        <v>6</v>
+      </c>
+      <c r="D312" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E312" s="1">
         <v>26.2</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E312" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B313" s="1">
+      <c r="B313" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C313" s="1">
+        <v>0</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E313" s="1">
         <v>22.7</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E313" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B314" s="1">
+      <c r="B314" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C314" s="1">
+        <v>1</v>
+      </c>
+      <c r="D314" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E314" s="1">
         <v>22</v>
-      </c>
-      <c r="C314" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E314" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B315" s="1">
+      <c r="B315" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C315" s="1">
+        <v>2</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E315" s="1">
         <v>21.8</v>
-      </c>
-      <c r="C315" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E315" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B316" s="1">
+      <c r="B316" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C316" s="1">
+        <v>3</v>
+      </c>
+      <c r="D316" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E316" s="1">
         <v>21.9</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E316" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B317" s="1">
+      <c r="B317" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C317" s="1">
+        <v>4</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E317" s="1">
         <v>22</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E317" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B318" s="1">
+      <c r="B318" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C318" s="1">
+        <v>5</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E318" s="1">
         <v>22</v>
-      </c>
-      <c r="C318" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E318" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B319" s="1">
+      <c r="B319" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C319" s="1">
+        <v>6</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E319" s="1">
         <v>22.6</v>
-      </c>
-      <c r="C319" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E319" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B320" s="1">
+      <c r="B320" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C320" s="1">
+        <v>0</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E320" s="1">
         <v>24.8</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E320" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B321" s="1">
+      <c r="B321" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C321" s="1">
+        <v>1</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E321" s="1">
         <v>26.2</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E321" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B322" s="1">
+      <c r="B322" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C322" s="1">
+        <v>2</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E322" s="1">
         <v>30.8</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E322" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B323" s="1">
+      <c r="B323" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C323" s="1">
+        <v>3</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E323" s="1">
         <v>31.3</v>
-      </c>
-      <c r="C323" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D323" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E323" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B324" s="1">
+      <c r="B324" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C324" s="1">
+        <v>4</v>
+      </c>
+      <c r="D324" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E324" s="1">
         <v>32.5</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E324" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B325" s="1">
+      <c r="B325" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C325" s="1">
+        <v>5</v>
+      </c>
+      <c r="D325" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E325" s="1">
         <v>32</v>
-      </c>
-      <c r="C325" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D325" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E325" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B326" s="1">
+      <c r="B326" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C326" s="1">
+        <v>6</v>
+      </c>
+      <c r="D326" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E326" s="1">
         <v>34.200000000000003</v>
-      </c>
-      <c r="C326" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D326" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E326" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B327" s="1">
+      <c r="B327" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C327" s="1">
+        <v>0</v>
+      </c>
+      <c r="D327" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E327" s="1">
         <v>23</v>
-      </c>
-      <c r="C327" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D327" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E327" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B328" s="1">
+      <c r="B328" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C328" s="1">
+        <v>1</v>
+      </c>
+      <c r="D328" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E328" s="1">
         <v>25.4</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D328" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E328" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B329" s="1">
+      <c r="B329" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C329" s="1">
+        <v>2</v>
+      </c>
+      <c r="D329" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E329" s="1">
         <v>28.2</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E329" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B330" s="1">
+      <c r="B330" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C330" s="1">
+        <v>3</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E330" s="1">
         <v>28.2</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E330" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B331" s="1">
+      <c r="B331" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C331" s="1">
+        <v>4</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E331" s="1">
         <v>29.5</v>
-      </c>
-      <c r="C331" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E331" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B332" s="1">
+      <c r="B332" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C332" s="1">
+        <v>5</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E332" s="1">
         <v>30.9</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E332" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B333" s="1">
+      <c r="B333" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C333" s="1">
+        <v>6</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E333" s="1">
         <v>30.8</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E333" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B334" s="1">
+      <c r="B334" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C334" s="1">
+        <v>0</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E334" s="1">
         <v>23.4</v>
-      </c>
-      <c r="C334" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E334" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B335" s="1">
+      <c r="B335" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C335" s="1">
+        <v>1</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E335" s="1">
         <v>25.2</v>
-      </c>
-      <c r="C335" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E335" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B336" s="1">
+      <c r="B336" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C336" s="1">
+        <v>2</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E336" s="1">
         <v>27.4</v>
-      </c>
-      <c r="C336" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E336" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B337" s="1">
+      <c r="B337" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C337" s="1">
+        <v>3</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E337" s="1">
         <v>28.8</v>
-      </c>
-      <c r="C337" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E337" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B338" s="1">
+      <c r="B338" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C338" s="1">
+        <v>4</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E338" s="1">
         <v>28</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D338" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E338" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B339" s="1">
+      <c r="B339" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C339" s="1">
+        <v>5</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E339" s="1">
         <v>28.8</v>
-      </c>
-      <c r="C339" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D339" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E339" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B340" s="1">
+      <c r="B340" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C340" s="1">
+        <v>6</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E340" s="1">
         <v>29.9</v>
-      </c>
-      <c r="C340" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E340" s="1">
-        <v>6</v>
       </c>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B341" s="1">
+      <c r="B341" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C341" s="1">
+        <v>0</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E341" s="1">
         <v>26</v>
-      </c>
-      <c r="C341" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E341" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B342" s="1">
+      <c r="B342" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C342" s="1">
+        <v>1</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E342" s="1">
         <v>28.1</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D342" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E342" s="1">
-        <v>1</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B343" s="1">
+      <c r="B343" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C343" s="1">
+        <v>2</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E343" s="1">
         <v>30.6</v>
-      </c>
-      <c r="C343" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E343" s="1">
-        <v>2</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B344" s="1">
+      <c r="B344" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C344" s="1">
+        <v>3</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E344" s="1">
         <v>31.7</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E344" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B345" s="1">
+      <c r="B345" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C345" s="1">
+        <v>4</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E345" s="1">
         <v>32</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E345" s="1">
-        <v>4</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B346" s="1">
+      <c r="B346" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C346" s="1">
+        <v>5</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E346" s="1">
         <v>33.700000000000003</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D346" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E346" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B347" s="1">
+      <c r="B347" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C347" s="1">
+        <v>6</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E347" s="1">
         <v>32.799999999999997</v>
-      </c>
-      <c r="C347" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D347" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E347" s="1">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
